--- a/Employee_Reports_wi48/Kevin Carl Enriquez Serrano Q0604.xlsx
+++ b/Employee_Reports_wi48/Kevin Carl Enriquez Serrano Q0604.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1301,11 +1301,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1350,11 +1350,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1399,11 +1399,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1436,11 +1436,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1485,11 +1485,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7945</v>
+        <v>7942</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7933</v>
+        <v>7930</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7933</v>
+        <v>7930</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7961</v>
+        <v>7958</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
